--- a/OHC_ensemble/observ_late/JMA/ohca_JMA.xlsx
+++ b/OHC_ensemble/observ_late/JMA/ohca_JMA.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_15_codefigurestats/OHC_ensemble/observ_late/JMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC046158-925A-E845-AF41-266D43A4CD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF37EA2-B375-D148-BACE-57036832A0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5900" yWindow="4700" windowWidth="26040" windowHeight="14940" xr2:uid="{AE373007-990D-6245-BCC9-B65117A52765}"/>
+    <workbookView xWindow="0" yWindow="5260" windowWidth="26040" windowHeight="14940" xr2:uid="{AE373007-990D-6245-BCC9-B65117A52765}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>E(0-2000)</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>0-2000m_allLat_se</t>
+  </si>
+  <si>
+    <t>A(0-700)</t>
+  </si>
+  <si>
+    <t>A(700-2000)</t>
   </si>
 </sst>
 </file>
@@ -419,10 +425,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ECE34A4-074F-834B-81F3-F9AE6A673002}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -432,49 +438,67 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1955</v>
       </c>
       <c r="B2">
-        <f>E2*10</f>
+        <f>D2*10</f>
         <v>0</v>
       </c>
       <c r="C2">
-        <f>F2/4*10</f>
+        <f>E2/4*10</f>
         <v>9.2249999999999996</v>
       </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
       <c r="E2">
+        <v>3.69</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1956</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B66" si="0">E3*10</f>
+        <f t="shared" ref="B3:B66" si="0">D3*10</f>
         <v>21.7</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C66" si="1">F3/4*10</f>
+        <f t="shared" ref="C3:C66" si="1">E3/4*10</f>
         <v>9.1750000000000007</v>
       </c>
+      <c r="D3">
+        <v>2.17</v>
+      </c>
       <c r="E3">
-        <v>2.17</v>
-      </c>
-      <c r="F3">
         <v>3.67</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J3">
+        <v>1.6</v>
+      </c>
+      <c r="K3">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1957</v>
       </c>
@@ -486,14 +510,20 @@
         <f t="shared" si="1"/>
         <v>9.1</v>
       </c>
+      <c r="D4">
+        <v>0.4</v>
+      </c>
       <c r="E4">
-        <v>0.4</v>
-      </c>
-      <c r="F4">
         <v>3.64</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J4">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K4">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1958</v>
       </c>
@@ -505,14 +535,20 @@
         <f t="shared" si="1"/>
         <v>9.0250000000000004</v>
       </c>
+      <c r="D5">
+        <v>4.07</v>
+      </c>
       <c r="E5">
-        <v>4.07</v>
-      </c>
-      <c r="F5">
         <v>3.61</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J5">
+        <v>3.79</v>
+      </c>
+      <c r="K5">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1959</v>
       </c>
@@ -524,14 +560,20 @@
         <f t="shared" si="1"/>
         <v>9.1</v>
       </c>
+      <c r="D6">
+        <v>2.25</v>
+      </c>
       <c r="E6">
-        <v>2.25</v>
-      </c>
-      <c r="F6">
         <v>3.64</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J6">
+        <v>2.15</v>
+      </c>
+      <c r="K6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1960</v>
       </c>
@@ -543,14 +585,20 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
+      <c r="D7">
+        <v>5.01</v>
+      </c>
       <c r="E7">
-        <v>5.01</v>
-      </c>
-      <c r="F7">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J7">
+        <v>3.81</v>
+      </c>
+      <c r="K7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1961</v>
       </c>
@@ -562,14 +610,20 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
+      <c r="D8">
+        <v>6.51</v>
+      </c>
       <c r="E8">
-        <v>6.51</v>
-      </c>
-      <c r="F8">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J8">
+        <v>5.45</v>
+      </c>
+      <c r="K8">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1962</v>
       </c>
@@ -581,14 +635,20 @@
         <f t="shared" si="1"/>
         <v>8.9249999999999989</v>
       </c>
+      <c r="D9">
+        <v>8.3800000000000008</v>
+      </c>
       <c r="E9">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="F9">
         <v>3.57</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J9">
+        <v>6.57</v>
+      </c>
+      <c r="K9">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1963</v>
       </c>
@@ -600,14 +660,20 @@
         <f t="shared" si="1"/>
         <v>8.875</v>
       </c>
+      <c r="D10">
+        <v>7.77</v>
+      </c>
       <c r="E10">
-        <v>7.77</v>
-      </c>
-      <c r="F10">
         <v>3.55</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J10">
+        <v>5.8</v>
+      </c>
+      <c r="K10">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1964</v>
       </c>
@@ -619,14 +685,20 @@
         <f t="shared" si="1"/>
         <v>8.8249999999999993</v>
       </c>
+      <c r="D11">
+        <v>7.44</v>
+      </c>
       <c r="E11">
-        <v>7.44</v>
-      </c>
-      <c r="F11">
         <v>3.53</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J11">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="K11">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1965</v>
       </c>
@@ -638,14 +710,20 @@
         <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
+      <c r="D12">
+        <v>7.51</v>
+      </c>
       <c r="E12">
-        <v>7.51</v>
-      </c>
-      <c r="F12">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J12">
+        <v>4.47</v>
+      </c>
+      <c r="K12">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1966</v>
       </c>
@@ -657,14 +735,20 @@
         <f t="shared" si="1"/>
         <v>8.7250000000000014</v>
       </c>
+      <c r="D13">
+        <v>8.49</v>
+      </c>
       <c r="E13">
-        <v>8.49</v>
-      </c>
-      <c r="F13">
         <v>3.49</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J13">
+        <v>5.17</v>
+      </c>
+      <c r="K13">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1967</v>
       </c>
@@ -676,14 +760,20 @@
         <f t="shared" si="1"/>
         <v>8.625</v>
       </c>
+      <c r="D14">
+        <v>5.81</v>
+      </c>
       <c r="E14">
-        <v>5.81</v>
-      </c>
-      <c r="F14">
         <v>3.45</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J14">
+        <v>3.66</v>
+      </c>
+      <c r="K14">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1968</v>
       </c>
@@ -695,14 +785,20 @@
         <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
+      <c r="D15">
+        <v>4.0199999999999996</v>
+      </c>
       <c r="E15">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="F15">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J15">
+        <v>2.42</v>
+      </c>
+      <c r="K15">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1969</v>
       </c>
@@ -714,14 +810,20 @@
         <f t="shared" si="1"/>
         <v>8.4749999999999996</v>
       </c>
+      <c r="D16">
+        <v>4.97</v>
+      </c>
       <c r="E16">
-        <v>4.97</v>
-      </c>
-      <c r="F16">
         <v>3.39</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J16">
+        <v>3.03</v>
+      </c>
+      <c r="K16">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1970</v>
       </c>
@@ -733,14 +835,20 @@
         <f t="shared" si="1"/>
         <v>8.4</v>
       </c>
+      <c r="D17">
+        <v>6.43</v>
+      </c>
       <c r="E17">
-        <v>6.43</v>
-      </c>
-      <c r="F17">
         <v>3.36</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J17">
+        <v>3.86</v>
+      </c>
+      <c r="K17">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1971</v>
       </c>
@@ -752,14 +860,20 @@
         <f t="shared" si="1"/>
         <v>8.1999999999999993</v>
       </c>
+      <c r="D18">
+        <v>8.83</v>
+      </c>
       <c r="E18">
-        <v>8.83</v>
-      </c>
-      <c r="F18">
         <v>3.28</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J18">
+        <v>5.32</v>
+      </c>
+      <c r="K18">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1972</v>
       </c>
@@ -771,14 +885,20 @@
         <f t="shared" si="1"/>
         <v>8.25</v>
       </c>
+      <c r="D19">
+        <v>8.1999999999999993</v>
+      </c>
       <c r="E19">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F19">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J19">
+        <v>6.16</v>
+      </c>
+      <c r="K19">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1973</v>
       </c>
@@ -790,14 +910,20 @@
         <f t="shared" si="1"/>
         <v>8.2750000000000004</v>
       </c>
+      <c r="D20">
+        <v>8.67</v>
+      </c>
       <c r="E20">
-        <v>8.67</v>
-      </c>
-      <c r="F20">
         <v>3.31</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J20">
+        <v>6.17</v>
+      </c>
+      <c r="K20">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1974</v>
       </c>
@@ -809,14 +935,20 @@
         <f t="shared" si="1"/>
         <v>8.4</v>
       </c>
+      <c r="D21">
+        <v>8.17</v>
+      </c>
       <c r="E21">
-        <v>8.17</v>
-      </c>
-      <c r="F21">
         <v>3.36</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J21">
+        <v>5.78</v>
+      </c>
+      <c r="K21">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1975</v>
       </c>
@@ -828,14 +960,20 @@
         <f t="shared" si="1"/>
         <v>8.4250000000000007</v>
       </c>
+      <c r="D22">
+        <v>10.87</v>
+      </c>
       <c r="E22">
-        <v>10.87</v>
-      </c>
-      <c r="F22">
         <v>3.37</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J22">
+        <v>7.18</v>
+      </c>
+      <c r="K22">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1976</v>
       </c>
@@ -847,14 +985,20 @@
         <f t="shared" si="1"/>
         <v>8.3249999999999993</v>
       </c>
+      <c r="D23">
+        <v>9.81</v>
+      </c>
       <c r="E23">
-        <v>9.81</v>
-      </c>
-      <c r="F23">
         <v>3.33</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J23">
+        <v>6.45</v>
+      </c>
+      <c r="K23">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1977</v>
       </c>
@@ -866,14 +1010,20 @@
         <f t="shared" si="1"/>
         <v>8.35</v>
       </c>
+      <c r="D24">
+        <v>9.74</v>
+      </c>
       <c r="E24">
-        <v>9.74</v>
-      </c>
-      <c r="F24">
         <v>3.34</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J24">
+        <v>6.34</v>
+      </c>
+      <c r="K24">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1978</v>
       </c>
@@ -885,14 +1035,20 @@
         <f t="shared" si="1"/>
         <v>8.2999999999999989</v>
       </c>
+      <c r="D25">
+        <v>9.85</v>
+      </c>
       <c r="E25">
-        <v>9.85</v>
-      </c>
-      <c r="F25">
         <v>3.32</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J25">
+        <v>6.68</v>
+      </c>
+      <c r="K25">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1979</v>
       </c>
@@ -904,14 +1060,20 @@
         <f t="shared" si="1"/>
         <v>8.1999999999999993</v>
       </c>
+      <c r="D26">
+        <v>10.17</v>
+      </c>
       <c r="E26">
-        <v>10.17</v>
-      </c>
-      <c r="F26">
         <v>3.28</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J26">
+        <v>7.3</v>
+      </c>
+      <c r="K26">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1980</v>
       </c>
@@ -923,14 +1085,20 @@
         <f t="shared" si="1"/>
         <v>8.125</v>
       </c>
+      <c r="D27">
+        <v>13.49</v>
+      </c>
       <c r="E27">
-        <v>13.49</v>
-      </c>
-      <c r="F27">
         <v>3.25</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J27">
+        <v>9.18</v>
+      </c>
+      <c r="K27">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1981</v>
       </c>
@@ -942,14 +1110,20 @@
         <f t="shared" si="1"/>
         <v>8.1499999999999986</v>
       </c>
+      <c r="D28">
+        <v>14.23</v>
+      </c>
       <c r="E28">
-        <v>14.23</v>
-      </c>
-      <c r="F28">
         <v>3.26</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J28">
+        <v>10.43</v>
+      </c>
+      <c r="K28">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1982</v>
       </c>
@@ -961,14 +1135,20 @@
         <f t="shared" si="1"/>
         <v>8.125</v>
       </c>
+      <c r="D29">
+        <v>12.05</v>
+      </c>
       <c r="E29">
-        <v>12.05</v>
-      </c>
-      <c r="F29">
         <v>3.25</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J29">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="K29">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1983</v>
       </c>
@@ -980,14 +1160,20 @@
         <f t="shared" si="1"/>
         <v>8.0749999999999993</v>
       </c>
+      <c r="D30">
+        <v>11.2</v>
+      </c>
       <c r="E30">
-        <v>11.2</v>
-      </c>
-      <c r="F30">
         <v>3.23</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J30">
+        <v>7.71</v>
+      </c>
+      <c r="K30">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1984</v>
       </c>
@@ -999,14 +1185,20 @@
         <f t="shared" si="1"/>
         <v>8.125</v>
       </c>
+      <c r="D31">
+        <v>12.48</v>
+      </c>
       <c r="E31">
-        <v>12.48</v>
-      </c>
-      <c r="F31">
         <v>3.25</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J31">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K31">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1985</v>
       </c>
@@ -1018,14 +1210,20 @@
         <f t="shared" si="1"/>
         <v>8.0250000000000004</v>
       </c>
+      <c r="D32">
+        <v>13.94</v>
+      </c>
       <c r="E32">
-        <v>13.94</v>
-      </c>
-      <c r="F32">
         <v>3.21</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J32">
+        <v>9.73</v>
+      </c>
+      <c r="K32">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1986</v>
       </c>
@@ -1037,14 +1235,20 @@
         <f t="shared" si="1"/>
         <v>8.0250000000000004</v>
       </c>
+      <c r="D33">
+        <v>14.16</v>
+      </c>
       <c r="E33">
-        <v>14.16</v>
-      </c>
-      <c r="F33">
         <v>3.21</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J33">
+        <v>9.15</v>
+      </c>
+      <c r="K33">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1987</v>
       </c>
@@ -1056,14 +1260,20 @@
         <f t="shared" si="1"/>
         <v>7.9</v>
       </c>
+      <c r="D34">
+        <v>12.29</v>
+      </c>
       <c r="E34">
-        <v>12.29</v>
-      </c>
-      <c r="F34">
         <v>3.16</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J34">
+        <v>8.36</v>
+      </c>
+      <c r="K34">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1988</v>
       </c>
@@ -1075,14 +1285,20 @@
         <f t="shared" si="1"/>
         <v>7.9249999999999998</v>
       </c>
+      <c r="D35">
+        <v>14.75</v>
+      </c>
       <c r="E35">
-        <v>14.75</v>
-      </c>
-      <c r="F35">
         <v>3.17</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J35">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="K35">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1989</v>
       </c>
@@ -1094,14 +1310,20 @@
         <f t="shared" si="1"/>
         <v>7.9749999999999996</v>
       </c>
+      <c r="D36">
+        <v>15</v>
+      </c>
       <c r="E36">
-        <v>15</v>
-      </c>
-      <c r="F36">
         <v>3.19</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J36">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="K36">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1990</v>
       </c>
@@ -1113,14 +1335,20 @@
         <f t="shared" si="1"/>
         <v>7.7749999999999995</v>
       </c>
+      <c r="D37">
+        <v>14.98</v>
+      </c>
       <c r="E37">
-        <v>14.98</v>
-      </c>
-      <c r="F37">
         <v>3.11</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J37">
+        <v>10.38</v>
+      </c>
+      <c r="K37">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1991</v>
       </c>
@@ -1132,14 +1360,20 @@
         <f t="shared" si="1"/>
         <v>7.7749999999999995</v>
       </c>
+      <c r="D38">
+        <v>16.07</v>
+      </c>
       <c r="E38">
-        <v>16.07</v>
-      </c>
-      <c r="F38">
         <v>3.11</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J38">
+        <v>11.19</v>
+      </c>
+      <c r="K38">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1992</v>
       </c>
@@ -1151,14 +1385,20 @@
         <f t="shared" si="1"/>
         <v>7.7</v>
       </c>
+      <c r="D39">
+        <v>18.71</v>
+      </c>
       <c r="E39">
-        <v>18.71</v>
-      </c>
-      <c r="F39">
         <v>3.08</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J39">
+        <v>12.25</v>
+      </c>
+      <c r="K39">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1993</v>
       </c>
@@ -1170,14 +1410,20 @@
         <f t="shared" si="1"/>
         <v>7.65</v>
       </c>
+      <c r="D40">
+        <v>18.95</v>
+      </c>
       <c r="E40">
-        <v>18.95</v>
-      </c>
-      <c r="F40">
         <v>3.06</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J40">
+        <v>12.03</v>
+      </c>
+      <c r="K40">
+        <v>6.92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1994</v>
       </c>
@@ -1189,14 +1435,20 @@
         <f t="shared" si="1"/>
         <v>7.7749999999999995</v>
       </c>
+      <c r="D41">
+        <v>19.07</v>
+      </c>
       <c r="E41">
-        <v>19.07</v>
-      </c>
-      <c r="F41">
         <v>3.11</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J41">
+        <v>12.22</v>
+      </c>
+      <c r="K41">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1995</v>
       </c>
@@ -1208,14 +1460,20 @@
         <f t="shared" si="1"/>
         <v>7.65</v>
       </c>
+      <c r="D42">
+        <v>16.149999999999999</v>
+      </c>
       <c r="E42">
-        <v>16.149999999999999</v>
-      </c>
-      <c r="F42">
         <v>3.06</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J42">
+        <v>10.48</v>
+      </c>
+      <c r="K42">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1996</v>
       </c>
@@ -1227,14 +1485,20 @@
         <f t="shared" si="1"/>
         <v>7.65</v>
       </c>
+      <c r="D43">
+        <v>19.13</v>
+      </c>
       <c r="E43">
-        <v>19.13</v>
-      </c>
-      <c r="F43">
         <v>3.06</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J43">
+        <v>12.47</v>
+      </c>
+      <c r="K43">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1997</v>
       </c>
@@ -1246,14 +1510,20 @@
         <f t="shared" si="1"/>
         <v>7.625</v>
       </c>
+      <c r="D44">
+        <v>19.86</v>
+      </c>
       <c r="E44">
-        <v>19.86</v>
-      </c>
-      <c r="F44">
         <v>3.05</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J44">
+        <v>12.58</v>
+      </c>
+      <c r="K44">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1998</v>
       </c>
@@ -1265,14 +1535,20 @@
         <f t="shared" si="1"/>
         <v>7.5749999999999993</v>
       </c>
+      <c r="D45">
+        <v>18.39</v>
+      </c>
       <c r="E45">
-        <v>18.39</v>
-      </c>
-      <c r="F45">
         <v>3.03</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J45">
+        <v>12.71</v>
+      </c>
+      <c r="K45">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1999</v>
       </c>
@@ -1284,14 +1560,20 @@
         <f t="shared" si="1"/>
         <v>7.5749999999999993</v>
       </c>
+      <c r="D46">
+        <v>21.6</v>
+      </c>
       <c r="E46">
-        <v>21.6</v>
-      </c>
-      <c r="F46">
         <v>3.03</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J46">
+        <v>14.7</v>
+      </c>
+      <c r="K46">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>2000</v>
       </c>
@@ -1303,14 +1585,20 @@
         <f t="shared" si="1"/>
         <v>7.625</v>
       </c>
+      <c r="D47">
+        <v>20.170000000000002</v>
+      </c>
       <c r="E47">
-        <v>20.170000000000002</v>
-      </c>
-      <c r="F47">
         <v>3.05</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J47">
+        <v>13.66</v>
+      </c>
+      <c r="K47">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2001</v>
       </c>
@@ -1322,14 +1610,20 @@
         <f t="shared" si="1"/>
         <v>7.625</v>
       </c>
+      <c r="D48">
+        <v>22.22</v>
+      </c>
       <c r="E48">
-        <v>22.22</v>
-      </c>
-      <c r="F48">
         <v>3.05</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J48">
+        <v>14.78</v>
+      </c>
+      <c r="K48">
+        <v>7.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>2002</v>
       </c>
@@ -1341,14 +1635,20 @@
         <f t="shared" si="1"/>
         <v>7.4750000000000005</v>
       </c>
+      <c r="D49">
+        <v>25.22</v>
+      </c>
       <c r="E49">
-        <v>25.22</v>
-      </c>
-      <c r="F49">
         <v>2.99</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J49">
+        <v>17.23</v>
+      </c>
+      <c r="K49">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>2003</v>
       </c>
@@ -1360,14 +1660,20 @@
         <f t="shared" si="1"/>
         <v>7.05</v>
       </c>
+      <c r="D50">
+        <v>28.38</v>
+      </c>
       <c r="E50">
-        <v>28.38</v>
-      </c>
-      <c r="F50">
         <v>2.82</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J50">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="K50">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>2004</v>
       </c>
@@ -1379,14 +1685,20 @@
         <f t="shared" si="1"/>
         <v>6.625</v>
       </c>
+      <c r="D51">
+        <v>27.74</v>
+      </c>
       <c r="E51">
-        <v>27.74</v>
-      </c>
-      <c r="F51">
         <v>2.65</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J51">
+        <v>18.53</v>
+      </c>
+      <c r="K51">
+        <v>9.2100000000000009</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>2005</v>
       </c>
@@ -1398,14 +1710,20 @@
         <f t="shared" si="1"/>
         <v>6.2250000000000005</v>
       </c>
+      <c r="D52">
+        <v>28.15</v>
+      </c>
       <c r="E52">
-        <v>28.15</v>
-      </c>
-      <c r="F52">
         <v>2.4900000000000002</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J52">
+        <v>18.36</v>
+      </c>
+      <c r="K52">
+        <v>9.7799999999999994</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>2006</v>
       </c>
@@ -1417,14 +1735,20 @@
         <f t="shared" si="1"/>
         <v>6.05</v>
       </c>
+      <c r="D53">
+        <v>29.53</v>
+      </c>
       <c r="E53">
-        <v>29.53</v>
-      </c>
-      <c r="F53">
         <v>2.42</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J53">
+        <v>19.12</v>
+      </c>
+      <c r="K53">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>2007</v>
       </c>
@@ -1436,14 +1760,20 @@
         <f t="shared" si="1"/>
         <v>5.9250000000000007</v>
       </c>
+      <c r="D54">
+        <v>27.71</v>
+      </c>
       <c r="E54">
-        <v>27.71</v>
-      </c>
-      <c r="F54">
         <v>2.37</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J54">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="K54">
+        <v>10.029999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>2008</v>
       </c>
@@ -1455,14 +1785,20 @@
         <f t="shared" si="1"/>
         <v>5.8</v>
       </c>
+      <c r="D55">
+        <v>29.49</v>
+      </c>
       <c r="E55">
-        <v>29.49</v>
-      </c>
-      <c r="F55">
         <v>2.3199999999999998</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J55">
+        <v>19.09</v>
+      </c>
+      <c r="K55">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>2009</v>
       </c>
@@ -1474,14 +1810,20 @@
         <f t="shared" si="1"/>
         <v>5.6749999999999998</v>
       </c>
+      <c r="D56">
+        <v>30.91</v>
+      </c>
       <c r="E56">
-        <v>30.91</v>
-      </c>
-      <c r="F56">
         <v>2.27</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J56">
+        <v>20.13</v>
+      </c>
+      <c r="K56">
+        <v>10.78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>2010</v>
       </c>
@@ -1493,14 +1835,20 @@
         <f t="shared" si="1"/>
         <v>5.6749999999999998</v>
       </c>
+      <c r="D57">
+        <v>31.08</v>
+      </c>
       <c r="E57">
-        <v>31.08</v>
-      </c>
-      <c r="F57">
         <v>2.27</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J57">
+        <v>20.02</v>
+      </c>
+      <c r="K57">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>2011</v>
       </c>
@@ -1512,14 +1860,20 @@
         <f t="shared" si="1"/>
         <v>5.6499999999999995</v>
       </c>
+      <c r="D58">
+        <v>32.49</v>
+      </c>
       <c r="E58">
-        <v>32.49</v>
-      </c>
-      <c r="F58">
         <v>2.2599999999999998</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J58">
+        <v>20.74</v>
+      </c>
+      <c r="K58">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>2012</v>
       </c>
@@ -1531,14 +1885,20 @@
         <f t="shared" si="1"/>
         <v>5.625</v>
       </c>
+      <c r="D59">
+        <v>32.75</v>
+      </c>
       <c r="E59">
-        <v>32.75</v>
-      </c>
-      <c r="F59">
         <v>2.25</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J59">
+        <v>20.52</v>
+      </c>
+      <c r="K59">
+        <v>12.23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>2013</v>
       </c>
@@ -1550,14 +1910,20 @@
         <f t="shared" si="1"/>
         <v>5.85</v>
       </c>
+      <c r="D60">
+        <v>35.61</v>
+      </c>
       <c r="E60">
-        <v>35.61</v>
-      </c>
-      <c r="F60">
         <v>2.34</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J60">
+        <v>22.35</v>
+      </c>
+      <c r="K60">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>2014</v>
       </c>
@@ -1569,14 +1935,20 @@
         <f t="shared" si="1"/>
         <v>5.85</v>
       </c>
+      <c r="D61">
+        <v>36.29</v>
+      </c>
       <c r="E61">
-        <v>36.29</v>
-      </c>
-      <c r="F61">
         <v>2.34</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J61">
+        <v>22.58</v>
+      </c>
+      <c r="K61">
+        <v>13.71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>2015</v>
       </c>
@@ -1588,14 +1960,20 @@
         <f t="shared" si="1"/>
         <v>5.7750000000000004</v>
       </c>
+      <c r="D62">
+        <v>38.22</v>
+      </c>
       <c r="E62">
-        <v>38.22</v>
-      </c>
-      <c r="F62">
         <v>2.31</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J62">
+        <v>24.02</v>
+      </c>
+      <c r="K62">
+        <v>14.21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>2016</v>
       </c>
@@ -1607,14 +1985,20 @@
         <f t="shared" si="1"/>
         <v>5.7750000000000004</v>
       </c>
+      <c r="D63">
+        <v>37.159999999999997</v>
+      </c>
       <c r="E63">
-        <v>37.159999999999997</v>
-      </c>
-      <c r="F63">
         <v>2.31</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J63">
+        <v>23.02</v>
+      </c>
+      <c r="K63">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>2017</v>
       </c>
@@ -1626,14 +2010,20 @@
         <f t="shared" si="1"/>
         <v>5.7750000000000004</v>
       </c>
+      <c r="D64">
+        <v>40.18</v>
+      </c>
       <c r="E64">
-        <v>40.18</v>
-      </c>
-      <c r="F64">
         <v>2.31</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J64">
+        <v>25.24</v>
+      </c>
+      <c r="K64">
+        <v>14.94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>2018</v>
       </c>
@@ -1645,14 +2035,20 @@
         <f t="shared" si="1"/>
         <v>5.8</v>
       </c>
+      <c r="D65">
+        <v>40.86</v>
+      </c>
       <c r="E65">
-        <v>40.86</v>
-      </c>
-      <c r="F65">
         <v>2.3199999999999998</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J65">
+        <v>26.14</v>
+      </c>
+      <c r="K65">
+        <v>14.73</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>2019</v>
       </c>
@@ -1664,33 +2060,45 @@
         <f t="shared" si="1"/>
         <v>5.875</v>
       </c>
+      <c r="D66">
+        <v>42.81</v>
+      </c>
       <c r="E66">
-        <v>42.81</v>
-      </c>
-      <c r="F66">
         <v>2.35</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J66">
+        <v>27.37</v>
+      </c>
+      <c r="K66">
+        <v>15.44</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2020</v>
       </c>
       <c r="B67">
-        <f t="shared" ref="B67:B71" si="2">E67*10</f>
+        <f t="shared" ref="B67:B72" si="2">D67*10</f>
         <v>433.1</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C71" si="3">F67/4*10</f>
+        <f t="shared" ref="C67:C72" si="3">E67/4*10</f>
         <v>5.9499999999999993</v>
       </c>
+      <c r="D67">
+        <v>43.31</v>
+      </c>
       <c r="E67">
-        <v>43.31</v>
-      </c>
-      <c r="F67">
         <v>2.38</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J67">
+        <v>27.57</v>
+      </c>
+      <c r="K67">
+        <v>15.74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>2021</v>
       </c>
@@ -1702,14 +2110,20 @@
         <f t="shared" si="3"/>
         <v>6.2</v>
       </c>
+      <c r="D68">
+        <v>45.06</v>
+      </c>
       <c r="E68">
-        <v>45.06</v>
-      </c>
-      <c r="F68">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J68">
+        <v>28.64</v>
+      </c>
+      <c r="K68">
+        <v>16.420000000000002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>2022</v>
       </c>
@@ -1721,14 +2135,20 @@
         <f t="shared" si="3"/>
         <v>6.3249999999999993</v>
       </c>
+      <c r="D69">
+        <v>46.77</v>
+      </c>
       <c r="E69">
-        <v>46.77</v>
-      </c>
-      <c r="F69">
         <v>2.5299999999999998</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J69">
+        <v>29.93</v>
+      </c>
+      <c r="K69">
+        <v>16.84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>2023</v>
       </c>
@@ -1740,30 +2160,67 @@
         <f t="shared" si="3"/>
         <v>6.2749999999999995</v>
       </c>
+      <c r="D70">
+        <v>46.58</v>
+      </c>
       <c r="E70">
-        <v>46.58</v>
-      </c>
-      <c r="F70">
         <v>2.5099999999999998</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J70">
+        <v>30.34</v>
+      </c>
+      <c r="K70">
+        <v>16.23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>2024</v>
       </c>
       <c r="B71">
         <f t="shared" si="2"/>
-        <v>488.40000000000003</v>
+        <v>488</v>
       </c>
       <c r="C71">
         <f t="shared" si="3"/>
         <v>6.3249999999999993</v>
       </c>
+      <c r="D71">
+        <v>48.8</v>
+      </c>
       <c r="E71">
-        <v>48.84</v>
-      </c>
-      <c r="F71">
         <v>2.5299999999999998</v>
+      </c>
+      <c r="J71">
+        <v>32.119999999999997</v>
+      </c>
+      <c r="K71">
+        <v>16.68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>2025</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="2"/>
+        <v>509.7</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="3"/>
+        <v>6.2250000000000005</v>
+      </c>
+      <c r="D72">
+        <v>50.97</v>
+      </c>
+      <c r="E72">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="J72">
+        <v>33.380000000000003</v>
+      </c>
+      <c r="K72">
+        <v>17.579999999999998</v>
       </c>
     </row>
   </sheetData>
